--- a/MMORPG_SERVER/Data/Excel/TaskDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/TaskDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECB4B53-B5B7-4761-A095-33FBF143FC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52FCCAF-E847-402C-95B8-43EAC1B2A9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>击败2只毒蝎龙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>尝试1次5连抽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,6 +80,18 @@
   </si>
   <si>
     <t>和村长进行对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewordCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成后的金币奖励数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击败1只毒蝎龙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -412,14 +420,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.875" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="4" max="4" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -429,8 +438,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -440,8 +452,11 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -451,110 +466,134 @@
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>

--- a/MMORPG_SERVER/Data/Excel/TaskDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/TaskDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52FCCAF-E847-402C-95B8-43EAC1B2A9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423EE67C-7C62-4F99-ADDF-9BC9998C22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,10 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>击败2只石头人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>和村长进行对话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,7 +87,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>击败1只毒蝎龙</t>
+    <t>击败2只怪物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -420,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.875" customWidth="1"/>
@@ -439,7 +435,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -453,7 +449,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -475,7 +471,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -489,10 +485,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1">
         <v>1000</v>
@@ -503,13 +499,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>2000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -517,7 +513,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -531,10 +527,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>500</v>
@@ -545,28 +541,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>500</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -597,11 +584,6 @@
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
